--- a/Data/EquipStatRange.xlsx
+++ b/Data/EquipStatRange.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A5A88E-F4C6-4649-994E-886FB77B6A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCDF4DC-FA6C-41DA-8132-5EA0DC088100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57495" yWindow="10440" windowWidth="19410" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipStatRange" sheetId="1" r:id="rId1"/>

--- a/Data/EquipStatRange.xlsx
+++ b/Data/EquipStatRange.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCDF4DC-FA6C-41DA-8132-5EA0DC088100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E4B3E5-287A-4D7A-AF7F-9E3020C4361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9375" yWindow="4590" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipStatRange" sheetId="1" r:id="rId1"/>
@@ -678,34 +678,34 @@
         <v>8</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="C5" s="3">
-        <v>3.5999999999999996</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="D5" s="3">
         <v>0.02</v>
       </c>
       <c r="E5" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F5" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.08</v>
       </c>
       <c r="G5" s="3">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H5" s="3">
-        <v>1.2E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I5" s="3">
-        <v>1.3999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="3">
-        <v>1.6E-2</v>
+        <v>0.16</v>
       </c>
       <c r="K5" s="3">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>10</v>
@@ -716,34 +716,34 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="C6" s="3">
-        <v>2.4</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D6" s="3">
         <v>0.02</v>
       </c>
       <c r="E6" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F6" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.08</v>
       </c>
       <c r="G6" s="3">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H6" s="3">
-        <v>1.2E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I6" s="3">
-        <v>1.3999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J6" s="3">
-        <v>1.6E-2</v>
+        <v>0.16</v>
       </c>
       <c r="K6" s="3">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>10</v>
@@ -754,34 +754,34 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="C7" s="3">
-        <v>2.4</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D7" s="3">
         <v>0.02</v>
       </c>
       <c r="E7" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F7" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.08</v>
       </c>
       <c r="G7" s="3">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="3">
-        <v>1.2E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I7" s="3">
-        <v>1.3999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J7" s="3">
-        <v>1.6E-2</v>
+        <v>0.16</v>
       </c>
       <c r="K7" s="3">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>10</v>
@@ -792,34 +792,34 @@
         <v>19</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="C8" s="3">
-        <v>2.4</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D8" s="3">
         <v>0.02</v>
       </c>
       <c r="E8" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F8" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="3">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H8" s="3">
-        <v>1.2E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I8" s="3">
-        <v>1.3999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J8" s="3">
-        <v>1.6E-2</v>
+        <v>0.16</v>
       </c>
       <c r="K8" s="3">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>10</v>
@@ -839,25 +839,25 @@
         <v>0.02</v>
       </c>
       <c r="E9">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F9">
-        <v>8.0000000000000002E-3</v>
+        <v>0.08</v>
       </c>
       <c r="G9">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H9">
-        <v>1.2E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I9">
-        <v>1.3999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J9">
-        <v>1.6E-2</v>
+        <v>0.16</v>
       </c>
       <c r="K9">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L9" t="s">
         <v>9</v>
@@ -877,25 +877,25 @@
         <v>0.02</v>
       </c>
       <c r="E10">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F10">
-        <v>8.0000000000000002E-3</v>
+        <v>0.08</v>
       </c>
       <c r="G10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H10">
-        <v>1.2E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I10">
-        <v>1.3999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J10">
-        <v>1.6E-2</v>
+        <v>0.16</v>
       </c>
       <c r="K10">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L10" t="s">
         <v>9</v>
